--- a/artfynd/A 42483-2025 artfynd.xlsx
+++ b/artfynd/A 42483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129129714</v>
       </c>
       <c r="B2" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129129713</v>
       </c>
       <c r="B3" t="n">
-        <v>92153</v>
+        <v>92158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129129715</v>
       </c>
       <c r="B4" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42483-2025 artfynd.xlsx
+++ b/artfynd/A 42483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129129714</v>
       </c>
       <c r="B2" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129129713</v>
       </c>
       <c r="B3" t="n">
-        <v>92158</v>
+        <v>92161</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129129715</v>
       </c>
       <c r="B4" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42483-2025 artfynd.xlsx
+++ b/artfynd/A 42483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129129714</v>
       </c>
       <c r="B2" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129129713</v>
       </c>
       <c r="B3" t="n">
-        <v>92161</v>
+        <v>92168</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129129715</v>
       </c>
       <c r="B4" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42483-2025 artfynd.xlsx
+++ b/artfynd/A 42483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129129714</v>
       </c>
       <c r="B2" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129129713</v>
       </c>
       <c r="B3" t="n">
-        <v>92168</v>
+        <v>92175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129129715</v>
       </c>
       <c r="B4" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42483-2025 artfynd.xlsx
+++ b/artfynd/A 42483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129129714</v>
       </c>
       <c r="B2" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129129713</v>
       </c>
       <c r="B3" t="n">
-        <v>92175</v>
+        <v>92177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129129715</v>
       </c>
       <c r="B4" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42483-2025 artfynd.xlsx
+++ b/artfynd/A 42483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129129714</v>
       </c>
       <c r="B2" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129129713</v>
       </c>
       <c r="B3" t="n">
-        <v>92177</v>
+        <v>92192</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129129715</v>
       </c>
       <c r="B4" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42483-2025 artfynd.xlsx
+++ b/artfynd/A 42483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129129714</v>
       </c>
       <c r="B2" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129129713</v>
       </c>
       <c r="B3" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129129715</v>
       </c>
       <c r="B4" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42483-2025 artfynd.xlsx
+++ b/artfynd/A 42483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129129714</v>
       </c>
       <c r="B2" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129129713</v>
       </c>
       <c r="B3" t="n">
-        <v>92193</v>
+        <v>92196</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129129715</v>
       </c>
       <c r="B4" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42483-2025 artfynd.xlsx
+++ b/artfynd/A 42483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129129714</v>
       </c>
       <c r="B2" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129129713</v>
       </c>
       <c r="B3" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129129715</v>
       </c>
       <c r="B4" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42483-2025 artfynd.xlsx
+++ b/artfynd/A 42483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129129714</v>
       </c>
       <c r="B2" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129129713</v>
       </c>
       <c r="B3" t="n">
-        <v>92198</v>
+        <v>92202</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129129715</v>
       </c>
       <c r="B4" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42483-2025 artfynd.xlsx
+++ b/artfynd/A 42483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129129714</v>
       </c>
       <c r="B2" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129129713</v>
       </c>
       <c r="B3" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129129715</v>
       </c>
       <c r="B4" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42483-2025 artfynd.xlsx
+++ b/artfynd/A 42483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129129714</v>
       </c>
       <c r="B2" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129129713</v>
       </c>
       <c r="B3" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129129715</v>
       </c>
       <c r="B4" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42483-2025 artfynd.xlsx
+++ b/artfynd/A 42483-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129129714</v>
       </c>
       <c r="B2" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>129129713</v>
       </c>
       <c r="B3" t="n">
-        <v>92206</v>
+        <v>92234</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129129715</v>
       </c>
       <c r="B4" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
